--- a/artfynd/A 17078-2024 artfynd.xlsx
+++ b/artfynd/A 17078-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89561670</v>
+        <v>89561590</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388566.0010105936</v>
+        <v>388520</v>
       </c>
       <c r="R2" t="n">
-        <v>6965996.929675938</v>
+        <v>6965977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89561639</v>
+        <v>89561635</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388897.1554749842</v>
+        <v>388636</v>
       </c>
       <c r="R3" t="n">
-        <v>6966233.77067633</v>
+        <v>6966114</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89561603</v>
+        <v>89561592</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388800.0522614125</v>
+        <v>388676</v>
       </c>
       <c r="R4" t="n">
-        <v>6966194.95324721</v>
+        <v>6966146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,16 +981,11 @@
         <v>89561669</v>
       </c>
       <c r="B5" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1048,12 +998,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388656.1080375597</v>
+        <v>388656</v>
       </c>
       <c r="R5" t="n">
-        <v>6965950.84698626</v>
+        <v>6965951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89561655</v>
+        <v>89561603</v>
       </c>
       <c r="B6" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388657.0702248048</v>
+        <v>388800</v>
       </c>
       <c r="R6" t="n">
-        <v>6965952.187485506</v>
+        <v>6966195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89561615</v>
+        <v>89561594</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388805.1344852477</v>
+        <v>388845</v>
       </c>
       <c r="R7" t="n">
-        <v>6966196.154088821</v>
+        <v>6966242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,14 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89561661</v>
+        <v>89561600</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388459.9446014598</v>
+        <v>388780</v>
       </c>
       <c r="R8" t="n">
-        <v>6965883.814390618</v>
+        <v>6966184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1354,14 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89561610</v>
+        <v>89561639</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388763.1496723021</v>
+        <v>388897</v>
       </c>
       <c r="R9" t="n">
-        <v>6966187.965569278</v>
+        <v>6966234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1460,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1493,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89561592</v>
+        <v>89561655</v>
       </c>
       <c r="B10" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388676.0219992503</v>
+        <v>388657</v>
       </c>
       <c r="R10" t="n">
-        <v>6966146.066841156</v>
+        <v>6965952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,19 +1561,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1594,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89561594</v>
+        <v>89561650</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388845.1841094918</v>
+        <v>388659</v>
       </c>
       <c r="R11" t="n">
-        <v>6966241.937857185</v>
+        <v>6965902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,24 +1662,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,243 +1688,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>89561650</v>
-      </c>
-      <c r="B12" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Söder om Uggvallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>388659.0424559803</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6965902.229505828</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>89561600</v>
-      </c>
-      <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Söder om Uggvallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>388779.9797274225</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6966184.191437902</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 17078-2024 artfynd.xlsx
+++ b/artfynd/A 17078-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561590</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561635</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561592</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561669</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561603</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561594</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561600</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561639</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561655</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,8 +1742,25 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561650</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>